--- a/셔틀버스_노선관리.xlsx
+++ b/셔틀버스_노선관리.xlsx
@@ -606,7 +606,7 @@
         <v>복지관</v>
       </c>
       <c r="E6" t="str">
-        <v>07:51</v>
+        <v>07:50</v>
       </c>
       <c r="F6" t="str">
         <v/>
